--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74094E0E-6618-4D27-ACFD-333FBEE7B7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3DAD4E-E08D-4060-89A7-6DF2F2EEC03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="diccionario" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>1054-2026</t>
   </si>
@@ -235,6 +235,54 @@
   </si>
   <si>
     <t>Requiere reprogramación</t>
+  </si>
+  <si>
+    <t>Preliminar (en reuniones y revisión previa)</t>
+  </si>
+  <si>
+    <t>req_reprogr_sustento</t>
+  </si>
+  <si>
+    <t>mma_estado</t>
+  </si>
+  <si>
+    <t>Demora en contratación o dispoinibilidad de profesionales clave u equipos</t>
+  </si>
+  <si>
+    <t>Demora en contratación o disponibilidad de profesionales clave u equipos.</t>
+  </si>
+  <si>
+    <t>Demora en adquisición, compras o contratación de bienes y servicios.</t>
+  </si>
+  <si>
+    <t>Demora en adquisición, compras o contratación de bienes y servicio.
+Demora en contratación o disponibilidad de profesionales clave (servicio de mantenimiento).
+Demora en autorización de insumos químicos fiscalizados.
+Ajustes de diseño.</t>
+  </si>
+  <si>
+    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras autorizaciones normativas.</t>
+  </si>
+  <si>
+    <t>Otros (Cite reprograma por asuntos internos)</t>
+  </si>
+  <si>
+    <t>Demora en adquisición, compras o contratación de bienes y servicios.
+Demora en contratación o dispoinibilidad de profesionales clave u equipos.</t>
+  </si>
+  <si>
+    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras autorizaciones normativas.
+Demora en adquisición, compras o contratación de bienes y servicios.</t>
+  </si>
+  <si>
+    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras auotriciones normativas.
+*Demora en adq, compras o contrat. de bs y ss</t>
+  </si>
+  <si>
+    <t>Motivos de la reprogramación</t>
+  </si>
+  <si>
+    <t>Estado de las Modificaciones de Menor Alcance</t>
   </si>
 </sst>
 </file>
@@ -245,7 +293,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,8 +316,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,8 +335,14 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -358,11 +417,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -398,6 +468,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,8 +799,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -715,10 +812,11 @@
     <col min="11" max="11" width="14.109375" customWidth="1"/>
     <col min="12" max="12" width="15.33203125" customWidth="1"/>
     <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="16" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="45.33203125" style="21" customWidth="1"/>
+    <col min="15" max="15" width="42.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
@@ -758,8 +856,14 @@
       <c r="M1" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -799,8 +903,14 @@
       <c r="M2" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -840,8 +950,10 @@
       <c r="M3" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="13"/>
+      <c r="O3" s="18"/>
+    </row>
+    <row r="4" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -881,8 +993,12 @@
       <c r="M4" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="19"/>
+    </row>
+    <row r="5" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -922,8 +1038,12 @@
       <c r="M5" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -963,8 +1083,14 @@
       <c r="M6" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1004,8 +1130,14 @@
       <c r="M7" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1045,8 +1177,14 @@
       <c r="M8" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1086,8 +1224,10 @@
       <c r="M9" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="N9" s="13"/>
+      <c r="O9" s="18"/>
+    </row>
+    <row r="10" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1127,8 +1267,10 @@
       <c r="M10" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="13"/>
+      <c r="O10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1168,8 +1310,10 @@
       <c r="M11" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="13"/>
+      <c r="O11" s="18"/>
+    </row>
+    <row r="12" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1209,8 +1353,10 @@
       <c r="M12" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="15"/>
+      <c r="O12" s="18"/>
+    </row>
+    <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1250,8 +1396,12 @@
       <c r="M13" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1291,8 +1441,12 @@
       <c r="M14" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14" s="20"/>
+    </row>
+    <row r="15" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1332,8 +1486,12 @@
       <c r="M15" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="O15" s="20"/>
+    </row>
+    <row r="16" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -1373,8 +1531,14 @@
       <c r="M16" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="N16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -1414,8 +1578,14 @@
       <c r="M17" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1455,8 +1625,14 @@
       <c r="M18" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -1496,6 +1672,8 @@
       <c r="M19" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G19">
@@ -1545,8 +1723,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A138854-8EA5-422D-AA90-16741E68D00C}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
@@ -1652,6 +1833,22 @@
         <v>64</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3DAD4E-E08D-4060-89A7-6DF2F2EEC03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7495839-1A7F-429D-9E8F-DEF9C0AB4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
   <si>
     <t>1054-2026</t>
   </si>
@@ -186,15 +186,9 @@
     <t>financ_prog</t>
   </si>
   <si>
-    <t>financ_cert</t>
-  </si>
-  <si>
     <t>financ_deven</t>
   </si>
   <si>
-    <t>financ_cert_pct</t>
-  </si>
-  <si>
     <t>financ_deven_pct</t>
   </si>
   <si>
@@ -222,15 +216,9 @@
     <t>Ejecución financiera programada</t>
   </si>
   <si>
-    <t>Ejecucion financiera certificada</t>
-  </si>
-  <si>
     <t>Ejecución financiera devengada</t>
   </si>
   <si>
-    <t>Porcentaje de ejecución financiera certificada</t>
-  </si>
-  <si>
     <t>Porcentaje de ejecución financiera devengada</t>
   </si>
   <si>
@@ -240,49 +228,76 @@
     <t>Preliminar (en reuniones y revisión previa)</t>
   </si>
   <si>
-    <t>req_reprogr_sustento</t>
-  </si>
-  <si>
     <t>mma_estado</t>
   </si>
   <si>
-    <t>Demora en contratación o dispoinibilidad de profesionales clave u equipos</t>
-  </si>
-  <si>
-    <t>Demora en contratación o disponibilidad de profesionales clave u equipos.</t>
-  </si>
-  <si>
-    <t>Demora en adquisición, compras o contratación de bienes y servicios.</t>
-  </si>
-  <si>
-    <t>Demora en adquisición, compras o contratación de bienes y servicio.
-Demora en contratación o disponibilidad de profesionales clave (servicio de mantenimiento).
-Demora en autorización de insumos químicos fiscalizados.
-Ajustes de diseño.</t>
-  </si>
-  <si>
-    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras autorizaciones normativas.</t>
-  </si>
-  <si>
-    <t>Otros (Cite reprograma por asuntos internos)</t>
-  </si>
-  <si>
-    <t>Demora en adquisición, compras o contratación de bienes y servicios.
-Demora en contratación o dispoinibilidad de profesionales clave u equipos.</t>
-  </si>
-  <si>
-    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras autorizaciones normativas.
-Demora en adquisición, compras o contratación de bienes y servicios.</t>
-  </si>
-  <si>
-    <t>Demora en aprobación de tarifario, autorizaciones DGO, OTI u otras auotriciones normativas.
-*Demora en adq, compras o contrat. de bs y ss</t>
-  </si>
-  <si>
-    <t>Motivos de la reprogramación</t>
-  </si>
-  <si>
     <t>Estado de las Modificaciones de Menor Alcance</t>
+  </si>
+  <si>
+    <t>Va a reprogramar algunas actividades debido a que a la fecha no cuentan con los profesionales, insumos e equipos necesarios para la correcta ejecución de actividades.</t>
+  </si>
+  <si>
+    <t>Sin embargo, es preciso mencionar que existe el riesgo que debido a la incompatibilidad de actividades del personal CAS se produzca algún retraso, se comunica esto para información y consideración</t>
+  </si>
+  <si>
+    <t>Tenían solo un postor para que brinde los servicios de 3 actividades programadas para el hito, cuando OA solicita al postor su propuesta, el postor ya no se encontraba disponible. El Cite tiene inconvenientes en ubicar otros postores con perfiles similares. Todo lo va a mover al hito 2</t>
+  </si>
+  <si>
+    <t>Algunas adquisiciones de servicios de terceros fueron emitidas durante el mes 2 de ejecución generando que la ejecución de las actividades arrastre atraso de 1 mes, el CITE está preparando una solicitud de MNA sobre sus actividades 1.2 y 1.4.</t>
+  </si>
+  <si>
+    <t>Dos actividades van a reprogramarse para el hito 2,.No material de hilo disponible y no tienen profesionales técnicos disponibles</t>
+  </si>
+  <si>
+    <t>Va a reprogramar debido a que a la fecha no cuenta con las órdenes de compra de insumos (medio de verificación solicitado para el cumplimiento de la actividad 1.1).</t>
+  </si>
+  <si>
+    <t>Se requerirá la reprogramación ya que a la fecha no ha logrado la contratación de los 3 TDR, Seguimiento, analista y eléctrico; ademáss 1 servicio de abril. A ese personal, el cual su contrato sale en agosto.</t>
+  </si>
+  <si>
+    <t>el CITE a la fecha 02/06/2026 aun no ha cumplido con subir su informacion actualizada al SIFEST. La información disponible es al corte del RSM1</t>
+  </si>
+  <si>
+    <t>De acuerdo a lo coordinado con el CITE están trabajando en el cumplimiento del Hito I.</t>
+  </si>
+  <si>
+    <t>El 27/05 recién se ha emitido la resolución ejecutiva de la incorporación del servicio de diagnóstico en su tarifario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El CITE tiene previsto solicitar una MMA asociada a la reasignación de presupuesto y de las metas físicas que no logrará cumplir en el hito 1 serán reprogramadas en el hito 2. </t>
+  </si>
+  <si>
+    <t>La UT cuenta con el inicio de un servicio especializado para la elaboración de 3 protocolos, los mismos que están relacionados para el entrenamiento que depende de la adquisición de equipos, los mismos que están en levantamiento de observaciones de las EETT. Razón por la que se presume una MMA</t>
+  </si>
+  <si>
+    <t>El 25/05 se ha emitido la orden de servicio para la ejecución de las acciones programadas para el mes 3 de acuerdo al cronograma de actividades. El servicio tiene una duración de 40 días. Asimismo, OA ha devuelto un TDR solicitando que el proveedor debe acreditar experiencia. (situación que no fue observada en la revisión previa de OA con la DGIE). Al 3 mes ha programado</t>
+  </si>
+  <si>
+    <t>Previas a las coordinaciones sostenidas con el CITE tiene previsto presentar en el transcurso de semana la solicitud de modificacion de menor alcance para poder cumplir con el Hito I.</t>
+  </si>
+  <si>
+    <t>De las 8 actividades programadas para el hito 1, 6 de ellas corresponden al RSM3. Con respecto a las otras 02 actividades (actividad 2.1 y 2.6),  la UT menciona que se va a reportar para el hito 1 como "en proceso" ya que no se va culminar de ejecutar porque actualmente se encuentra en proceso el nuevo requerimiento, dado la situación la UT solicitará modificación de menor alcance.</t>
+  </si>
+  <si>
+    <t>Se cumplirá con las actividades programadas sin inconvenientes en el HITO 1</t>
+  </si>
+  <si>
+    <t>Detalles</t>
+  </si>
+  <si>
+    <t>Ejecucion financiera comprometida</t>
+  </si>
+  <si>
+    <t>Porcentaje de ejecución financiera comprometida</t>
+  </si>
+  <si>
+    <t>financ_compr</t>
+  </si>
+  <si>
+    <t>financ_compr_pct</t>
+  </si>
+  <si>
+    <t>detalles</t>
   </si>
 </sst>
 </file>
@@ -293,7 +308,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,25 +316,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="4">
@@ -432,69 +465,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,7 +856,7 @@
     <col min="11" max="11" width="14.109375" customWidth="1"/>
     <col min="12" max="12" width="15.33203125" customWidth="1"/>
     <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="14" width="45.33203125" style="21" customWidth="1"/>
+    <col min="14" max="14" width="42.6640625" style="18" customWidth="1"/>
     <col min="15" max="15" width="42.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -841,26 +885,26 @@
       <c r="H1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>67</v>
+      <c r="N1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -904,10 +948,10 @@
         <v>38</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -950,8 +994,10 @@
       <c r="M3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="18"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="22" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
@@ -993,10 +1039,10 @@
       <c r="M4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="19"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="23" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
@@ -1038,10 +1084,10 @@
       <c r="M5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="19"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="23" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
@@ -1083,11 +1129,11 @@
       <c r="M6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>65</v>
+      <c r="N6" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -1130,11 +1176,11 @@
       <c r="M7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>65</v>
+      <c r="N7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1178,10 +1224,10 @@
         <v>38</v>
       </c>
       <c r="N8" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>70</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1224,8 +1270,10 @@
       <c r="M9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="18"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="22" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
@@ -1267,8 +1315,8 @@
       <c r="M10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="18"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
@@ -1310,8 +1358,8 @@
       <c r="M11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="18"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
@@ -1354,7 +1402,9 @@
         <v>39</v>
       </c>
       <c r="N12" s="15"/>
-      <c r="O12" s="18"/>
+      <c r="O12" s="22" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
@@ -1396,10 +1446,10 @@
       <c r="M13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="O13" s="19"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="23" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
@@ -1441,10 +1491,10 @@
       <c r="M14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="O14" s="20"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="24" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
@@ -1486,10 +1536,10 @@
       <c r="M15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="O15" s="20"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="24" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="16" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
@@ -1532,10 +1582,10 @@
         <v>38</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="O16" s="20" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1579,10 +1629,10 @@
         <v>38</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1626,10 +1676,10 @@
         <v>38</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1672,8 +1722,10 @@
       <c r="M19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="18"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="22" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G19">
@@ -1742,7 +1794,7 @@
         <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1750,7 +1802,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1758,7 +1810,7 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1766,7 +1818,7 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1774,7 +1826,7 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1782,7 +1834,7 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1790,63 +1842,63 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
+      <c r="A9" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
+      <c r="A11" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
+      <c r="A15" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7495839-1A7F-429D-9E8F-DEF9C0AB4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8E7F9D-D5C3-4AC4-8F03-9EC81312753E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="90">
   <si>
     <t>1054-2026</t>
   </si>
@@ -234,27 +234,9 @@
     <t>Estado de las Modificaciones de Menor Alcance</t>
   </si>
   <si>
-    <t>Va a reprogramar algunas actividades debido a que a la fecha no cuentan con los profesionales, insumos e equipos necesarios para la correcta ejecución de actividades.</t>
-  </si>
-  <si>
     <t>Sin embargo, es preciso mencionar que existe el riesgo que debido a la incompatibilidad de actividades del personal CAS se produzca algún retraso, se comunica esto para información y consideración</t>
   </si>
   <si>
-    <t>Tenían solo un postor para que brinde los servicios de 3 actividades programadas para el hito, cuando OA solicita al postor su propuesta, el postor ya no se encontraba disponible. El Cite tiene inconvenientes en ubicar otros postores con perfiles similares. Todo lo va a mover al hito 2</t>
-  </si>
-  <si>
-    <t>Algunas adquisiciones de servicios de terceros fueron emitidas durante el mes 2 de ejecución generando que la ejecución de las actividades arrastre atraso de 1 mes, el CITE está preparando una solicitud de MNA sobre sus actividades 1.2 y 1.4.</t>
-  </si>
-  <si>
-    <t>Dos actividades van a reprogramarse para el hito 2,.No material de hilo disponible y no tienen profesionales técnicos disponibles</t>
-  </si>
-  <si>
-    <t>Va a reprogramar debido a que a la fecha no cuenta con las órdenes de compra de insumos (medio de verificación solicitado para el cumplimiento de la actividad 1.1).</t>
-  </si>
-  <si>
-    <t>Se requerirá la reprogramación ya que a la fecha no ha logrado la contratación de los 3 TDR, Seguimiento, analista y eléctrico; ademáss 1 servicio de abril. A ese personal, el cual su contrato sale en agosto.</t>
-  </si>
-  <si>
     <t>el CITE a la fecha 02/06/2026 aun no ha cumplido con subir su informacion actualizada al SIFEST. La información disponible es al corte del RSM1</t>
   </si>
   <si>
@@ -264,18 +246,6 @@
     <t>El 27/05 recién se ha emitido la resolución ejecutiva de la incorporación del servicio de diagnóstico en su tarifario.</t>
   </si>
   <si>
-    <t xml:space="preserve">El CITE tiene previsto solicitar una MMA asociada a la reasignación de presupuesto y de las metas físicas que no logrará cumplir en el hito 1 serán reprogramadas en el hito 2. </t>
-  </si>
-  <si>
-    <t>La UT cuenta con el inicio de un servicio especializado para la elaboración de 3 protocolos, los mismos que están relacionados para el entrenamiento que depende de la adquisición de equipos, los mismos que están en levantamiento de observaciones de las EETT. Razón por la que se presume una MMA</t>
-  </si>
-  <si>
-    <t>El 25/05 se ha emitido la orden de servicio para la ejecución de las acciones programadas para el mes 3 de acuerdo al cronograma de actividades. El servicio tiene una duración de 40 días. Asimismo, OA ha devuelto un TDR solicitando que el proveedor debe acreditar experiencia. (situación que no fue observada en la revisión previa de OA con la DGIE). Al 3 mes ha programado</t>
-  </si>
-  <si>
-    <t>Previas a las coordinaciones sostenidas con el CITE tiene previsto presentar en el transcurso de semana la solicitud de modificacion de menor alcance para poder cumplir con el Hito I.</t>
-  </si>
-  <si>
     <t>De las 8 actividades programadas para el hito 1, 6 de ellas corresponden al RSM3. Con respecto a las otras 02 actividades (actividad 2.1 y 2.6),  la UT menciona que se va a reportar para el hito 1 como "en proceso" ya que no se va culminar de ejecutar porque actualmente se encuentra en proceso el nuevo requerimiento, dado la situación la UT solicitará modificación de menor alcance.</t>
   </si>
   <si>
@@ -298,6 +268,48 @@
   </si>
   <si>
     <t>detalles</t>
+  </si>
+  <si>
+    <t>eje_hito</t>
+  </si>
+  <si>
+    <t>servicio</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>financ_cert</t>
+  </si>
+  <si>
+    <t>financ_cert_pct</t>
+  </si>
+  <si>
+    <t>No cuentan con los profesionales, insumos e equipos necesarios para la correcta ejecución de actividades.</t>
+  </si>
+  <si>
+    <t>Un postor para los servicios de 3 actividades programadas para el hito, inconveniente para encontrar perfiles</t>
+  </si>
+  <si>
+    <t>Servicios de terceros programadas para el mes 1  por retrasos se programaron al mes 2 de ejecución actividades 1.2 y 1.4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difucltades para conseguir material de hilo y profesionales técnicos </t>
+  </si>
+  <si>
+    <t>No cuenta con las órdenes de compra de insumos (medio de verificación solicitado para el cumplimiento de la actividad 1.1</t>
+  </si>
+  <si>
+    <t>N ha logrado la contratación de los 3 TDR, Seguimiento, analista y eléctrico; ademáss 1 servicio de abril. A ese personal, el cual su contrato sale en agosto.</t>
+  </si>
+  <si>
+    <t>Cite postergó inicio de actividades</t>
+  </si>
+  <si>
+    <t>Dificultades para la adquisición de equipos, los mismos que están en levantamiento de observaciones de las EETT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OA ha devuelto un TDR solicitando que el proveedor debe acreditar experiencia. (situación que no fue observada en la revisión previa de OA con la DGIE). </t>
   </si>
 </sst>
 </file>
@@ -308,11 +320,18 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -465,79 +484,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -843,24 +871,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
     <col min="3" max="3" width="38.6640625" customWidth="1"/>
     <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="14.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="14" width="42.6640625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="42.6640625" style="21" customWidth="1"/>
+    <col min="5" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" style="28" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="14" width="14.88671875" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.109375" customWidth="1"/>
+    <col min="17" max="17" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" customWidth="1"/>
+    <col min="19" max="19" width="42.6640625" style="18" customWidth="1"/>
+    <col min="20" max="20" width="42.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
@@ -880,34 +910,49 @@
         <v>45</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="12" t="s">
+      <c r="L1" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="O1" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="P1" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T1" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -924,37 +969,52 @@
         <v>14</v>
       </c>
       <c r="F2" s="5">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5">
         <v>6</v>
       </c>
-      <c r="G2" s="6">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="29">
+        <v>139</v>
+      </c>
+      <c r="J2" s="29">
+        <v>105</v>
+      </c>
+      <c r="K2" s="7">
         <v>158350</v>
       </c>
-      <c r="I2" s="7">
+      <c r="L2" s="7">
         <v>46616</v>
       </c>
-      <c r="J2" s="7">
-        <v>1056</v>
-      </c>
-      <c r="K2" s="8">
-        <v>0.29438585412061891</v>
-      </c>
-      <c r="L2" s="8">
-        <v>6.6687717082412378E-3</v>
-      </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="7">
+        <v>39092</v>
+      </c>
+      <c r="N2" s="7">
+        <v>7002</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0.24687085569940007</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0.24687085569940007</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>4.4218503315440479E-2</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T2" s="20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -971,35 +1031,50 @@
         <v>4</v>
       </c>
       <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="H3" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I3" s="29">
+        <v>7</v>
+      </c>
+      <c r="J3" s="29">
+        <v>7</v>
+      </c>
+      <c r="K3" s="7">
         <v>96950</v>
       </c>
-      <c r="I3" s="7">
-        <v>77492.44</v>
-      </c>
-      <c r="J3" s="7">
-        <v>11736.24</v>
-      </c>
-      <c r="K3" s="8">
-        <v>0.79930314595152141</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0.12105456420835482</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="L3" s="7">
+        <v>83372.44</v>
+      </c>
+      <c r="M3" s="7">
+        <v>82868.44</v>
+      </c>
+      <c r="N3" s="7">
+        <v>18736.240000000002</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0.8547544094894276</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0.8547544094894276</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0.19325673027333679</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="15"/>
+      <c r="T3" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1018,33 +1093,48 @@
       <c r="F4" s="5">
         <v>0</v>
       </c>
-      <c r="G4" s="11">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0</v>
+      </c>
+      <c r="I4" s="30">
+        <v>0</v>
+      </c>
+      <c r="J4" s="30">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
         <v>151913</v>
       </c>
-      <c r="I4" s="7">
-        <v>29876.26</v>
-      </c>
-      <c r="J4" s="7">
-        <v>4730.12</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0.19666690803288722</v>
-      </c>
-      <c r="L4" s="8">
-        <v>3.1137032380375608E-2</v>
-      </c>
-      <c r="M4" s="9" t="s">
+      <c r="L4" s="7">
+        <v>30645.11</v>
+      </c>
+      <c r="M4" s="7">
+        <v>14220.13</v>
+      </c>
+      <c r="N4" s="7">
+        <v>5629.42</v>
+      </c>
+      <c r="O4" s="8">
+        <v>9.3607064569852474E-2</v>
+      </c>
+      <c r="P4" s="8">
+        <v>9.3607064569852474E-2</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>3.7056868075806548E-2</v>
+      </c>
+      <c r="R4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="16"/>
-      <c r="O4" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S4" s="16"/>
+      <c r="T4" s="23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1061,35 +1151,50 @@
         <v>7</v>
       </c>
       <c r="F5" s="5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="5">
         <v>4</v>
       </c>
-      <c r="G5" s="11">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="H5" s="11">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I5" s="30">
+        <v>18</v>
+      </c>
+      <c r="J5" s="30">
+        <v>16</v>
+      </c>
+      <c r="K5" s="7">
         <v>156838</v>
       </c>
-      <c r="I5" s="7">
-        <v>81259</v>
-      </c>
-      <c r="J5" s="7">
+      <c r="L5" s="7">
+        <v>97331</v>
+      </c>
+      <c r="M5" s="7">
+        <v>88657</v>
+      </c>
+      <c r="N5" s="7">
         <v>14488.59</v>
       </c>
-      <c r="K5" s="8">
-        <v>0.51810785651436519</v>
-      </c>
-      <c r="L5" s="8">
+      <c r="O5" s="8">
+        <v>0.56527754753312331</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0.56527754753312331</v>
+      </c>
+      <c r="Q5" s="8">
         <v>9.2379334089952692E-2</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="R5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="16"/>
-      <c r="O5" s="23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S5" s="16"/>
+      <c r="T5" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1106,37 +1211,52 @@
         <v>13</v>
       </c>
       <c r="F6" s="5">
-        <v>4</v>
-      </c>
-      <c r="G6" s="11">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="I6" s="30">
+        <v>0</v>
+      </c>
+      <c r="J6" s="30">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
         <v>217442</v>
       </c>
-      <c r="I6" s="7">
+      <c r="L6" s="7">
         <v>90152</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0.41460251469357345</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="7">
+        <v>87580</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0.40277407308615631</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0.40277407308615631</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="S6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T6" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1155,35 +1275,50 @@
       <c r="F7" s="5">
         <v>0</v>
       </c>
-      <c r="G7" s="11">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="30">
+        <v>0</v>
+      </c>
+      <c r="J7" s="30">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
         <v>223105</v>
       </c>
-      <c r="I7" s="7">
+      <c r="L7" s="7">
         <v>76791</v>
       </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0.34419219649940613</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="7">
+        <v>14778</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8">
+        <v>6.6237870061181953E-2</v>
+      </c>
+      <c r="P7" s="8">
+        <v>6.6237870061181953E-2</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="S7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O7" s="20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T7" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1200,37 +1335,52 @@
         <v>8</v>
       </c>
       <c r="F8" s="5">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="H8" s="7">
+      <c r="H8" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="30">
+        <v>6</v>
+      </c>
+      <c r="J8" s="30">
+        <v>5</v>
+      </c>
+      <c r="K8" s="7">
         <v>40975</v>
       </c>
-      <c r="I8" s="7">
+      <c r="L8" s="7">
         <v>24500</v>
       </c>
-      <c r="J8" s="7">
+      <c r="M8" s="7">
+        <v>24000</v>
+      </c>
+      <c r="N8" s="7">
         <v>5500</v>
       </c>
-      <c r="K8" s="8">
-        <v>0.5979255643685174</v>
-      </c>
-      <c r="L8" s="8">
+      <c r="O8" s="8">
+        <v>0.58572300183038439</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0.58572300183038439</v>
+      </c>
+      <c r="Q8" s="8">
         <v>0.13422818791946309</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="S8" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O8" s="20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T8" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1247,35 +1397,50 @@
         <v>3</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1</v>
+      </c>
+      <c r="I9" s="30">
+        <v>87</v>
+      </c>
+      <c r="J9" s="30">
+        <v>66</v>
+      </c>
+      <c r="K9" s="7">
         <v>96875</v>
       </c>
-      <c r="I9" s="7">
+      <c r="L9" s="7">
         <v>73700</v>
       </c>
-      <c r="J9" s="7">
-        <v>43250</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0.76077419354838705</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0.44645161290322583</v>
-      </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="7">
+        <v>73000</v>
+      </c>
+      <c r="N9" s="7">
+        <v>46550</v>
+      </c>
+      <c r="O9" s="8">
+        <v>0.75354838709677419</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0.75354838709677419</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0.48051612903225804</v>
+      </c>
+      <c r="R9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S9" s="15"/>
+      <c r="T9" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1294,31 +1459,46 @@
       <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
         <v>0.2</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I10" s="29">
+        <v>0</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
         <v>89665</v>
       </c>
-      <c r="I10" s="7">
-        <v>48841</v>
-      </c>
-      <c r="J10" s="7">
+      <c r="L10" s="7">
+        <v>60075</v>
+      </c>
+      <c r="M10" s="7">
+        <v>60075</v>
+      </c>
+      <c r="N10" s="7">
         <v>4455</v>
       </c>
-      <c r="K10" s="8">
-        <v>0.54470529191992412</v>
-      </c>
-      <c r="L10" s="8">
+      <c r="O10" s="8">
+        <v>0.66999386605698996</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0.66999386605698996</v>
+      </c>
+      <c r="Q10" s="8">
         <v>4.9684938381754307E-2</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="R10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="15"/>
-      <c r="O10" s="22"/>
-    </row>
-    <row r="11" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="15"/>
+      <c r="T10" s="22"/>
+    </row>
+    <row r="11" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1335,33 +1515,48 @@
         <v>8</v>
       </c>
       <c r="F11" s="5">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5">
         <v>4</v>
       </c>
-      <c r="G11" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I11" s="29">
+        <v>540</v>
+      </c>
+      <c r="J11" s="29">
+        <v>22</v>
+      </c>
+      <c r="K11" s="7">
         <v>78375</v>
       </c>
-      <c r="I11" s="7">
+      <c r="L11" s="7">
         <v>69000</v>
       </c>
-      <c r="J11" s="7">
+      <c r="M11" s="7">
+        <v>67950</v>
+      </c>
+      <c r="N11" s="7">
         <v>25650</v>
       </c>
-      <c r="K11" s="8">
-        <v>0.88038277511961727</v>
-      </c>
-      <c r="L11" s="8">
+      <c r="O11" s="8">
+        <v>0.8669856459330143</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0.8669856459330143</v>
+      </c>
+      <c r="Q11" s="8">
         <v>0.32727272727272727</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="R11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="22"/>
-    </row>
-    <row r="12" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S11" s="15"/>
+      <c r="T11" s="22"/>
+    </row>
+    <row r="12" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1380,33 +1575,48 @@
       <c r="F12" s="5">
         <v>0</v>
       </c>
-      <c r="G12" s="11">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="30">
+        <v>0</v>
+      </c>
+      <c r="J12" s="30">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
         <v>21631</v>
       </c>
-      <c r="I12" s="7">
+      <c r="L12" s="7">
         <v>7280</v>
       </c>
-      <c r="J12" s="7">
+      <c r="M12" s="7">
+        <v>4000</v>
+      </c>
+      <c r="N12" s="7">
         <v>2000</v>
       </c>
-      <c r="K12" s="8">
-        <v>0.33655401969395776</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="O12" s="8">
+        <v>0.18491979104063613</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0.18491979104063613</v>
+      </c>
+      <c r="Q12" s="8">
         <v>9.2459895520318067E-2</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="R12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="15"/>
-      <c r="O12" s="22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S12" s="15"/>
+      <c r="T12" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1423,35 +1633,50 @@
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="30">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
         <v>70675</v>
       </c>
-      <c r="I13" s="7">
-        <v>50439.58</v>
-      </c>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0.71368348072161303</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="s">
+      <c r="L13" s="7">
+        <v>66939.58</v>
+      </c>
+      <c r="M13" s="7">
+        <v>57780.75</v>
+      </c>
+      <c r="N13" s="7">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0.8175557127697205</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0.8175557127697205</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="16"/>
-      <c r="O13" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S13" s="16"/>
+      <c r="T13" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1468,35 +1693,50 @@
         <v>13</v>
       </c>
       <c r="F14" s="5">
+        <v>5</v>
+      </c>
+      <c r="G14" s="5">
         <v>4</v>
       </c>
-      <c r="G14" s="11">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="H14" s="11">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="I14" s="30">
+        <v>13</v>
+      </c>
+      <c r="J14" s="30">
+        <v>5</v>
+      </c>
+      <c r="K14" s="7">
         <v>56175</v>
       </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="s">
+      <c r="L14" s="7">
+        <v>45000</v>
+      </c>
+      <c r="M14" s="7">
+        <v>45000</v>
+      </c>
+      <c r="N14" s="7">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11">
+        <v>0.8010680907877169</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0.8010680907877169</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N14" s="17"/>
-      <c r="O14" s="24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S14" s="17"/>
+      <c r="T14" s="24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1515,33 +1755,48 @@
       <c r="F15" s="5">
         <v>0</v>
       </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7">
         <v>109375</v>
       </c>
-      <c r="I15" s="7">
+      <c r="L15" s="7">
         <v>48042</v>
       </c>
-      <c r="J15" s="7">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0.43924114285714283</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="7">
+        <v>45000</v>
+      </c>
+      <c r="N15" s="7">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.41142857142857142</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.41142857142857142</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S15" s="17"/>
+      <c r="T15" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -1560,35 +1815,50 @@
       <c r="F16" s="5">
         <v>0</v>
       </c>
-      <c r="G16" s="11">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="30">
+        <v>0</v>
+      </c>
+      <c r="J16" s="30">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
         <v>159704</v>
       </c>
-      <c r="I16" s="7">
-        <v>62972.68</v>
-      </c>
-      <c r="J16" s="7">
-        <v>19972.68</v>
-      </c>
-      <c r="K16" s="8">
-        <v>0.39430872113409809</v>
-      </c>
-      <c r="L16" s="8">
-        <v>0.12506061213244501</v>
-      </c>
-      <c r="M16" s="9" t="s">
+      <c r="L16" s="7">
+        <v>63771.72</v>
+      </c>
+      <c r="M16" s="7">
+        <v>59680.72</v>
+      </c>
+      <c r="N16" s="7">
+        <v>21691.68</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0.37369583729900319</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0.37369583729900319</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0.13582427490858087</v>
+      </c>
+      <c r="R16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="S16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O16" s="20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T16" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -1607,35 +1877,48 @@
       <c r="F17" s="5">
         <v>2</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="5">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H17" s="7">
+      <c r="I17" s="29">
+        <v>91</v>
+      </c>
+      <c r="J17" s="29">
+        <v>13</v>
+      </c>
+      <c r="K17" s="7">
         <v>230221</v>
       </c>
-      <c r="I17" s="7">
+      <c r="L17" s="7">
         <v>10846</v>
       </c>
-      <c r="J17" s="7">
+      <c r="M17" s="7">
+        <v>10750</v>
+      </c>
+      <c r="N17" s="7">
         <v>4737.5</v>
       </c>
-      <c r="K17" s="8">
-        <v>4.7111253969012383E-2</v>
-      </c>
-      <c r="L17" s="8">
+      <c r="O17" s="8">
+        <v>4.669426333827062E-2</v>
+      </c>
+      <c r="P17" s="8">
+        <v>4.669426333827062E-2</v>
+      </c>
+      <c r="Q17" s="8">
         <v>2.0578053261865771E-2</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="R17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="S17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O17" s="20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T17" s="20"/>
+    </row>
+    <row r="18" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1652,37 +1935,52 @@
         <v>8</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.125</v>
+      </c>
+      <c r="I18" s="30">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
         <v>109175</v>
       </c>
-      <c r="I18" s="7">
+      <c r="L18" s="7">
         <v>58873.8</v>
       </c>
-      <c r="J18" s="7">
-        <v>16343.8</v>
-      </c>
-      <c r="K18" s="8">
-        <v>0.53926081978474927</v>
-      </c>
-      <c r="L18" s="8">
-        <v>0.14970277078085642</v>
-      </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="7">
+        <v>52873.8</v>
+      </c>
+      <c r="N18" s="7">
+        <v>33643.800000000003</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0.48430318296313263</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.48430318296313263</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0.30816395694985116</v>
+      </c>
+      <c r="R18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="S18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O18" s="20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T18" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -1699,36 +1997,51 @@
         <v>12</v>
       </c>
       <c r="F19" s="5">
+        <v>7</v>
+      </c>
+      <c r="G19" s="5">
         <v>4</v>
       </c>
-      <c r="G19" s="8">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="H19" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I19" s="29">
+        <v>165</v>
+      </c>
+      <c r="J19" s="29">
+        <v>74</v>
+      </c>
+      <c r="K19" s="7">
         <v>95775</v>
       </c>
-      <c r="I19" s="7">
+      <c r="L19" s="7">
         <v>87700</v>
       </c>
-      <c r="J19" s="7">
-        <v>10700</v>
-      </c>
-      <c r="K19" s="8">
+      <c r="M19" s="7">
+        <v>87700</v>
+      </c>
+      <c r="N19" s="7">
+        <v>22900</v>
+      </c>
+      <c r="O19" s="8">
         <v>0.91568780997128685</v>
       </c>
-      <c r="L19" s="8">
-        <v>0.11172017749934743</v>
-      </c>
-      <c r="M19" s="9" t="s">
+      <c r="P19" s="8">
+        <v>0.91568780997128685</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0.23910206212477161</v>
+      </c>
+      <c r="R19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="22" t="s">
-        <v>79</v>
+      <c r="S19" s="15"/>
+      <c r="T19" s="22" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="H2:J19">
     <cfRule type="cellIs" dxfId="10" priority="1" stopIfTrue="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -1746,7 +2059,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L19">
+  <conditionalFormatting sqref="O2:Q19">
     <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
@@ -1847,10 +2160,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1863,10 +2176,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1895,10 +2208,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F7D2BB-05EB-4B89-AB5E-C8AC86F0571E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2734D496-9B18-4116-8D14-79BF67534BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>1054-2026</t>
   </si>
@@ -225,6 +225,9 @@
     <t>Requiere reprogramación</t>
   </si>
   <si>
+    <t>Preliminar (en reuniones y revisión previa)</t>
+  </si>
+  <si>
     <t>mma_estado</t>
   </si>
   <si>
@@ -289,9 +292,6 @@
   </si>
   <si>
     <t>Dificultades para la adquisición de equipos, los mismos que están en levantamiento de observaciones de las EETT.</t>
-  </si>
-  <si>
-    <t>Si Aprobado</t>
   </si>
   <si>
     <t>Difucltades para conseguir material de hilo y profesionales técnicos</t>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>--</t>
+  </si>
+  <si>
+    <t>Aprobado (elaboración de informe a emitir)</t>
+  </si>
+  <si>
+    <t>Demora en adquisición de equipo heperbarico, debido a los tiempos de contratación de mayor cuantía, así como su fabricación, importación y desaduanaje.</t>
   </si>
 </sst>
 </file>
@@ -321,11 +327,18 @@
     <numFmt numFmtId="8" formatCode="&quot;S/&quot;\ #,##0.00;[Red]\-&quot;S/&quot;\ #,##0.00"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -401,9 +414,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -412,23 +425,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -708,28 +725,28 @@
         <v>46</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="10" t="s">
-        <v>76</v>
+      <c r="K1" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>48</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>49</v>
@@ -738,10 +755,10 @@
         <v>50</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -796,8 +813,11 @@
       <c r="Q2" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>39</v>
+      <c r="R2" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -846,11 +866,11 @@
       <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>83</v>
+      <c r="R3" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -899,8 +919,8 @@
       <c r="Q4" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>83</v>
+      <c r="R4" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S4" s="5" t="s">
         <v>84</v>
@@ -952,8 +972,8 @@
       <c r="Q5" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="3" t="s">
-        <v>39</v>
+      <c r="R5" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S5" s="5" t="s">
         <v>85</v>
@@ -1011,8 +1031,8 @@
       <c r="Q6" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="3" t="s">
-        <v>39</v>
+      <c r="R6" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S6" s="15" t="s">
         <v>86</v>
@@ -1070,8 +1090,8 @@
       <c r="Q7" t="s">
         <v>38</v>
       </c>
-      <c r="R7" s="3" t="s">
-        <v>39</v>
+      <c r="R7" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>87</v>
@@ -1123,11 +1143,11 @@
       <c r="Q8" t="s">
         <v>38</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>39</v>
+      <c r="R8" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1176,11 +1196,11 @@
       <c r="Q9" t="s">
         <v>38</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R9" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1230,7 +1250,7 @@
         <v>38</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>88</v>
@@ -1288,11 +1308,8 @@
       <c r="Q11" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1347,11 +1364,8 @@
       <c r="Q12" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1406,11 +1420,8 @@
       <c r="Q13" t="s">
         <v>39</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1459,9 +1470,6 @@
       <c r="Q14" t="s">
         <v>39</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S14" s="5" t="s">
         <v>89</v>
       </c>
@@ -1518,9 +1526,6 @@
       <c r="Q15" t="s">
         <v>39</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="16" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -1568,11 +1573,11 @@
       <c r="Q16" t="s">
         <v>38</v>
       </c>
-      <c r="R16" s="3" t="s">
-        <v>39</v>
+      <c r="R16" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1627,11 +1632,11 @@
       <c r="Q17" t="s">
         <v>38</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>39</v>
+      <c r="R17" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1686,11 +1691,11 @@
       <c r="Q18" t="s">
         <v>38</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>39</v>
+      <c r="R18" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1739,11 +1744,8 @@
       <c r="Q19" t="s">
         <v>39</v>
       </c>
-      <c r="R19" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S19" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1826,10 +1828,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1842,10 +1844,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1866,18 +1868,18 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2734D496-9B18-4116-8D14-79BF67534BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF80B58-5028-4B80-97B3-5BF114AB0B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
   <si>
     <t>1054-2026</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>Demora en adquisición de equipo heperbarico, debido a los tiempos de contratación de mayor cuantía, así como su fabricación, importación y desaduanaje.</t>
+  </si>
+  <si>
+    <t>Incidencias reportadas</t>
   </si>
 </sst>
 </file>
@@ -327,11 +330,18 @@
     <numFmt numFmtId="8" formatCode="&quot;S/&quot;\ #,##0.00;[Red]\-&quot;S/&quot;\ #,##0.00"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -414,9 +424,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -425,28 +435,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1878,8 +1889,8 @@
       <c r="A15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>69</v>
+      <c r="B15" s="18" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF80B58-5028-4B80-97B3-5BF114AB0B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4F4A03-5012-4B68-B77A-2B455B6B795E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -288,12 +288,6 @@
     <t>N ha logrado la contratación de los 3 TDR, Seguimiento, analista y eléctrico; ademáss 1 servicio de abril. A ese personal, el cual su contrato sale en agosto.</t>
   </si>
   <si>
-    <t>Cite postergó inicio de actividades</t>
-  </si>
-  <si>
-    <t>Dificultades para la adquisición de equipos, los mismos que están en levantamiento de observaciones de las EETT.</t>
-  </si>
-  <si>
     <t>Difucltades para conseguir material de hilo y profesionales técnicos</t>
   </si>
   <si>
@@ -307,9 +301,6 @@
     <t>Servicios de terceros programadas para el mes 1 por retrasos se programaron al mes 2 de ejecución actividades 1.2 y 1.4.</t>
   </si>
   <si>
-    <t>De las 8 actividades programadas para el hito 1, 6 de ellas corresponden al RSM3. Con respecto a las otras 02 actividades (actividad 2.1 y 2.6), la UT menciona que se va a reportar para el hito 1 como "en proceso" ya que no se va culminar de ejecutar porque actualmente se encuentra en proceso el nuevo requerimiento, dado la situación la UT solicitará modificación de menor alcance.</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -320,15 +311,26 @@
   </si>
   <si>
     <t>Incidencias reportadas</t>
+  </si>
+  <si>
+    <t>Dificultades para la adquisición de equipos/insumos para de ensayos de laboratorio, los mismos que están en levantamiento de observaciones de las EETT.</t>
+  </si>
+  <si>
+    <t>La UT Lima tiene 06 actividades para el Hito 1, 02 actividades se modificaron debido a que se cambió la denominación de las consultorías para que no ingresen al PDP</t>
+  </si>
+  <si>
+    <t>De lo antes señalado, se evidencia que, el sustento de modificación del cronograma del proyecto se sustenta principalmente, a factores asociados a condiciones de clima
+con presencia de lluvias en la región Loreto y disponibilidad de Unidades Productivas para la prestación de los servicios programados en el proyecto.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;S/&quot;\ #,##0.00;[Red]\-&quot;S/&quot;\ #,##0.00"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -424,7 +426,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -446,7 +448,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -458,10 +459,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -744,7 +746,7 @@
       <c r="J1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>77</v>
       </c>
       <c r="L1" s="7" t="s">
@@ -788,10 +790,10 @@
       <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="18">
         <v>2</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>0.66700000000000004</v>
       </c>
       <c r="H2" s="9">
@@ -800,35 +802,35 @@
       <c r="I2" s="9">
         <v>13</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>230221</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>230125</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>10750</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="13">
         <v>8238</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="11">
         <v>1</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="11">
         <v>4.7E-2</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="11">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="Q2" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>90</v>
+      <c r="R2" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -847,38 +849,38 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="18">
         <v>0</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>223105</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>26758</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
         <v>21778</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
         <v>1400</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <v>0.12</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="11">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="17" t="s">
-        <v>90</v>
+      <c r="R3" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>80</v>
@@ -900,41 +902,41 @@
       <c r="E4">
         <v>13</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="18">
         <v>6</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.46200000000000002</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>217442</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>87580</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>87580</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>0</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>0.40300000000000002</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="11">
         <v>0.40300000000000002</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <v>0</v>
       </c>
       <c r="Q4" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="17" t="s">
-        <v>90</v>
+      <c r="R4" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,41 +955,41 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="18">
         <v>0</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>0</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>159704</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>116743</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>116743</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>24898</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="11">
         <v>0.73099999999999998</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="11">
         <v>0.73099999999999998</v>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="11">
         <v>0.156</v>
       </c>
       <c r="Q5" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="17" t="s">
-        <v>90</v>
+      <c r="R5" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1006,10 +1008,10 @@
       <c r="E6">
         <v>14</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="18">
         <v>12</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>0.85699999999999998</v>
       </c>
       <c r="H6" s="9">
@@ -1018,35 +1020,35 @@
       <c r="I6" s="9">
         <v>105</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>158350</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>79392</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>79392</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <v>11802</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="11">
         <v>0.501</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="11">
         <v>0.501</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="11">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="Q6" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="S6" s="15" t="s">
-        <v>86</v>
+      <c r="R6" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1065,47 +1067,47 @@
       <c r="E7">
         <v>7</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="18">
         <v>6</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>0.85699999999999998</v>
       </c>
       <c r="H7" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I7" s="9">
-        <v>16</v>
-      </c>
-      <c r="J7" s="14">
+        <v>20</v>
+      </c>
+      <c r="J7" s="13">
         <v>156838</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>112636</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>112636</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
         <v>21968</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="11">
         <v>0.71799999999999997</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="11">
         <v>0.71799999999999997</v>
       </c>
-      <c r="P7" s="12">
+      <c r="P7" s="11">
         <v>0.14000000000000001</v>
       </c>
       <c r="Q7" t="s">
         <v>38</v>
       </c>
-      <c r="R7" s="17" t="s">
-        <v>90</v>
+      <c r="R7" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,38 +1126,38 @@
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="18">
         <v>0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>0</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>147913</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>21617</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>21611</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
         <v>12494</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
         <v>0.14599999999999999</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="11">
         <v>0.14599999999999999</v>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="11">
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="Q8" t="s">
         <v>38</v>
       </c>
-      <c r="R8" s="17" t="s">
-        <v>90</v>
+      <c r="R8" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>79</v>
@@ -1177,41 +1179,41 @@
       <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="18">
+        <v>4</v>
+      </c>
+      <c r="G9" s="12">
         <v>1</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>109375</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>45000</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="13">
         <v>45000</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="11">
         <v>0.41099999999999998</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="11">
         <v>0.41099999999999998</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="11">
         <v>0</v>
       </c>
       <c r="Q9" t="s">
         <v>38</v>
       </c>
-      <c r="R9" s="17" t="s">
+      <c r="R9" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1230,31 +1232,31 @@
       <c r="E10">
         <v>8</v>
       </c>
-      <c r="F10" s="11">
-        <v>8</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="F10" s="18">
+        <v>6</v>
+      </c>
+      <c r="G10" s="12">
         <v>1</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>103175</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>52874</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="13">
         <v>52874</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="13">
         <v>38594</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11">
         <v>0.51200000000000001</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="11">
         <v>0.51200000000000001</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="11">
         <v>0.374</v>
       </c>
       <c r="Q10" t="s">
@@ -1264,7 +1266,7 @@
         <v>61</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1283,10 +1285,10 @@
       <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="18">
         <v>4</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>1</v>
       </c>
       <c r="H11" s="9">
@@ -1295,25 +1297,25 @@
       <c r="I11" s="9">
         <v>7</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>96950</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>96355</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="13">
         <v>96355</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="13">
         <v>23736</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
         <v>0.99399999999999999</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="11">
         <v>0.99399999999999999</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="11">
         <v>0.245</v>
       </c>
       <c r="Q11" t="s">
@@ -1339,37 +1341,37 @@
       <c r="E12">
         <v>3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="18">
         <v>3</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>1</v>
       </c>
       <c r="H12" s="9">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" s="9">
-        <v>66</v>
-      </c>
-      <c r="J12" s="14">
+        <v>67</v>
+      </c>
+      <c r="J12" s="13">
         <v>96875</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>85400</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="13">
         <v>85400</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="13">
         <v>59000</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
         <v>0.88200000000000001</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="11">
         <v>0.88200000000000001</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="11">
         <v>0.60899999999999999</v>
       </c>
       <c r="Q12" t="s">
@@ -1395,37 +1397,37 @@
       <c r="E13">
         <v>12</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="18">
         <v>12</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>1</v>
       </c>
       <c r="H13" s="9">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="I13" s="9">
         <v>74</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>95775</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>87700</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
         <v>87700</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="13">
         <v>25900</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="11">
         <v>0.91600000000000004</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="11">
         <v>0.91600000000000004</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="11">
         <v>0.27</v>
       </c>
       <c r="Q13" t="s">
@@ -1451,38 +1453,38 @@
       <c r="E14">
         <v>5</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="18">
         <v>5</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>1</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>89665</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>65474</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="13">
         <v>60075</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="13">
         <v>8910</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="11">
         <v>0.73</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="11">
         <v>0.67</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="11">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="Q14" t="s">
         <v>39</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1501,10 +1503,10 @@
       <c r="E15">
         <v>8</v>
       </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15" s="13">
+      <c r="F15" s="18">
+        <v>8</v>
+      </c>
+      <c r="G15" s="12">
         <v>0.75</v>
       </c>
       <c r="H15" s="9">
@@ -1513,25 +1515,25 @@
       <c r="I15" s="9">
         <v>22</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>78375</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>67950</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="13">
         <v>67950</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="13">
         <v>41300</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="11">
         <v>0.86699999999999999</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="11">
         <v>0.86699999999999999</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P15" s="11">
         <v>0.52700000000000002</v>
       </c>
       <c r="Q15" t="s">
@@ -1554,38 +1556,38 @@
       <c r="E16">
         <v>4</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="18">
         <v>2</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>0.5</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>70675</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>64403</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="13">
         <v>64403</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="11">
         <v>0.91100000000000003</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="11">
         <v>0.91100000000000003</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="11">
         <v>0</v>
       </c>
       <c r="Q16" t="s">
         <v>38</v>
       </c>
-      <c r="R16" s="17" t="s">
-        <v>90</v>
+      <c r="R16" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S16" s="5" t="s">
         <v>67</v>
@@ -1607,10 +1609,10 @@
       <c r="E17">
         <v>13</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="18">
         <v>7</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>0.53800000000000003</v>
       </c>
       <c r="H17" s="9">
@@ -1619,35 +1621,35 @@
       <c r="I17" s="9">
         <v>5</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>56175</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>45000</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="13">
         <v>45000</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="13">
         <v>0</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="11">
         <v>0.80100000000000005</v>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="11">
         <v>0.80100000000000005</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="11">
         <v>0</v>
       </c>
       <c r="Q17" t="s">
         <v>38</v>
       </c>
-      <c r="R17" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>82</v>
+      <c r="R17" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1666,44 +1668,44 @@
       <c r="E18">
         <v>8</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="18">
         <v>5</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>0.625</v>
       </c>
       <c r="H18" s="9">
+        <v>7</v>
+      </c>
+      <c r="I18" s="9">
         <v>6</v>
       </c>
-      <c r="I18" s="9">
-        <v>5</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>40975</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>26000</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="13">
         <v>26000</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="13">
         <v>5500</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="11">
         <v>0.63500000000000001</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="11">
         <v>0.63500000000000001</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="11">
         <v>0.13400000000000001</v>
       </c>
       <c r="Q18" t="s">
         <v>38</v>
       </c>
-      <c r="R18" s="17" t="s">
-        <v>90</v>
+      <c r="R18" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="S18" s="5" t="s">
         <v>81</v>
@@ -1725,31 +1727,31 @@
       <c r="E19">
         <v>2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="18">
         <v>2</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <v>1</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>19131</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>12925</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="13">
         <v>12925</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="13">
         <v>2000</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="11">
         <v>0.67600000000000005</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="11">
         <v>0.67600000000000005</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="11">
         <v>0.105</v>
       </c>
       <c r="Q19" t="s">
@@ -1889,8 +1891,8 @@
       <c r="A15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>92</v>
+      <c r="B15" s="17" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4F4A03-5012-4B68-B77A-2B455B6B795E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF264C2E-656E-4436-8410-476A383E3D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
   <si>
     <t>1054-2026</t>
   </si>
@@ -183,12 +183,6 @@
     <t>fisica_pct</t>
   </si>
   <si>
-    <t>financ_prog</t>
-  </si>
-  <si>
-    <t>financ_deven</t>
-  </si>
-  <si>
     <t>financ_deven_pct</t>
   </si>
   <si>
@@ -213,42 +207,18 @@
     <t>Porcentaje de ejecución física ejecutada</t>
   </si>
   <si>
-    <t>Ejecución financiera programada</t>
-  </si>
-  <si>
-    <t>Ejecución financiera devengada</t>
-  </si>
-  <si>
     <t>Porcentaje de ejecución financiera devengada</t>
   </si>
   <si>
     <t>Requiere reprogramación</t>
   </si>
   <si>
-    <t>Preliminar (en reuniones y revisión previa)</t>
-  </si>
-  <si>
     <t>mma_estado</t>
   </si>
   <si>
     <t>Estado de las Modificaciones de Menor Alcance</t>
   </si>
   <si>
-    <t>Sin embargo, es preciso mencionar que existe el riesgo que debido a la incompatibilidad de actividades del personal CAS se produzca algún retraso, se comunica esto para información y consideración</t>
-  </si>
-  <si>
-    <t>el CITE a la fecha 02/06/2026 aun no ha cumplido con subir su informacion actualizada al SIFEST. La información disponible es al corte del RSM1</t>
-  </si>
-  <si>
-    <t>De acuerdo a lo coordinado con el CITE están trabajando en el cumplimiento del Hito I.</t>
-  </si>
-  <si>
-    <t>El 27/05 recién se ha emitido la resolución ejecutiva de la incorporación del servicio de diagnóstico en su tarifario.</t>
-  </si>
-  <si>
-    <t>Se cumplirá con las actividades programadas sin inconvenientes en el HITO 1</t>
-  </si>
-  <si>
     <t>Detalles</t>
   </si>
   <si>
@@ -279,48 +249,98 @@
     <t>financ_cert_pct</t>
   </si>
   <si>
-    <t>Un postor para los servicios de 3 actividades programadas para el hito, inconveniente para encontrar perfiles</t>
-  </si>
-  <si>
-    <t>No cuenta con las órdenes de compra de insumos (medio de verificación solicitado para el cumplimiento de la actividad 1.1</t>
-  </si>
-  <si>
-    <t>N ha logrado la contratación de los 3 TDR, Seguimiento, analista y eléctrico; ademáss 1 servicio de abril. A ese personal, el cual su contrato sale en agosto.</t>
-  </si>
-  <si>
-    <t>Difucltades para conseguir material de hilo y profesionales técnicos</t>
-  </si>
-  <si>
-    <t>OA ha devuelto un TDR solicitando que el proveedor debe acreditar experiencia. (situación que no fue observada en la revisión previa de OA con la DGIE).</t>
-  </si>
-  <si>
-    <t>Reprograma actividades 1.5 y 1.10 del mes 2 al mes 4, debido a retrasos en la adquisición de insumos, materiales y equipos.
-La demora también se originó por observaciones a las EE.TT., actualización de TDR/EETT por la nueva directiva de contratos menores y disponibilidad de especialistas..</t>
-  </si>
-  <si>
-    <t>Servicios de terceros programadas para el mes 1 por retrasos se programaron al mes 2 de ejecución actividades 1.2 y 1.4.</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>Aprobado (elaboración de informe a emitir)</t>
-  </si>
-  <si>
-    <t>Demora en adquisición de equipo heperbarico, debido a los tiempos de contratación de mayor cuantía, así como su fabricación, importación y desaduanaje.</t>
-  </si>
-  <si>
     <t>Incidencias reportadas</t>
   </si>
   <si>
-    <t>Dificultades para la adquisición de equipos/insumos para de ensayos de laboratorio, los mismos que están en levantamiento de observaciones de las EETT.</t>
-  </si>
-  <si>
-    <t>La UT Lima tiene 06 actividades para el Hito 1, 02 actividades se modificaron debido a que se cambió la denominación de las consultorías para que no ingresen al PDP</t>
-  </si>
-  <si>
-    <t>De lo antes señalado, se evidencia que, el sustento de modificación del cronograma del proyecto se sustenta principalmente, a factores asociados a condiciones de clima
-con presencia de lluvias en la región Loreto y disponibilidad de Unidades Productivas para la prestación de los servicios programados en el proyecto.</t>
+    <t>monto_desemb</t>
+  </si>
+  <si>
+    <t>presup_modif</t>
+  </si>
+  <si>
+    <t>presup_modifc</t>
+  </si>
+  <si>
+    <t>financ_deven_oa</t>
+  </si>
+  <si>
+    <t>Ejecución financiera devengada Oficina Administración</t>
+  </si>
+  <si>
+    <t>Aprobado</t>
+  </si>
+  <si>
+    <t>Al cierre del Hito 1, el proyecto muestra avances importantes en la validación y optimización del sistema biotecnológico en campo. Se superaron las metas técnicas programadas, ejecutando 13 asistencias técnicas frente a 4 previstas y 90 ensayos de laboratorio frente a 40 programados.
+En el aspecto financiero, se realizaron contrataciones de servicios clave, incluyendo un especialista acuícola y un coordinador administrativo. Asimismo, se acreditó la contrapartida mediante la participación del coordinador general y del analista de laboratorio durante tres meses.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el proyecto registró avances preparatorios y de gestión técnica para viabilizar las actividades experimentales previstas; sin embargo, no logró completar la ejecución física programada debido a modificaciones de cronograma y presupuesto, así como a la dependencia de insumos especializados y mantenimiento de equipos. La ejecución financiera alcanzó S/ 16,900.00, equivalente al 7% de lo programado, por lo que se plantea una reprogramación técnica y financiera sin alterar metas, productos ni objetivos del proyecto.</t>
+  </si>
+  <si>
+    <t>Durante la ejecución del proyecto se identificaron barreras técnicas y administrativas que afectaron el desarrollo oportuno de algunas actividades, principalmente por retrasos en la contratación de especialistas, observaciones a los TDR, limitada disponibilidad de profesionales con experiencia en fibra de vicuña y dependencia técnica entre las etapas de transformación de la fibra.
+Ante ello, el equipo técnico realizó acciones de seguimiento permanente, reformuló los TDR, coordinó con las áreas administrativas, gestionó la búsqueda de especialistas y tramitó una Modificación de Menor Alcance para reprogramar las actividades afectadas. Estas medidas permitieron sostener la continuidad del proyecto, concluir las actividades priorizadas y dejar debidamente sustentada la reprogramación de las actividades pendientes, proyectando el cumplimiento de las metas sin afectar los objetivos aprobados.s</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1 se avanzó principalmente en acciones preparatorias para fortalecer los servicios tecnológicos del CITE Productivo San Martín, incluyendo la elaboración de TDR y EETT, el inicio de contrataciones especializadas, la adquisición parcial de insumos y la valorización de la contrapartida.
+La ejecución financiera fue de S/ 40,700.72, equivalente al 10.61% del presupuesto del hito. La menor ejecución se explica por la reprogramación de actividades al Hito 2, sin afectar los objetivos, metas físicas ni presupuesto del proyecto.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el proyecto del CITEproductivo VRAEM cumplió y superó las metas físicas en 10 de 12 actividades, brindando 85 capacitaciones especializadas y 133 charlas técnicas en las cadenas de café, cacao y frutas, atendiendo a 149 unidades productivas.
+Dos actividades fueron reprogramadas por estacionalidad de cosecha y ajustes de cronograma. En lo financiero, se ejecutaron S/ 56,202.00, equivalentes al 28.13% del presupuesto del hito y al 14.98% del presupuesto total del proyecto.</t>
+  </si>
+  <si>
+    <t>El proyecto busca fortalecer capacidades técnicas y promover la adopción tecnológica en las cadenas acuícola y agroindustrial de Ucayali, beneficiando a 60 unidades productivas.
+Durante el Hito 1 surgieron retrasos por el desistimiento de un profesional, nuevos procesos de contratación y cronogramas que excedían el cierre del hito. Por ello, el 10 de junio de 2026 se presentó una solicitud de cambios para reprogramar actividades entre los Hitos 1 y 2.
+La reprogramación no modificó metas, indicadores, presupuesto, beneficiarios ni desembolsos; permitió alinear la ejecución a los plazos reales y asegurar la continuidad del proyecto.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, se logró contratar al especialista responsable de los servicios de diagnóstico situacional y se realizaron adquisiciones clave para la ejecución del proyecto, como banners, material informativo, botella Niskin, kit colorimétrico, útiles de oficina, materiales de bioseguridad, limpieza, desinfección, kits de disección y ecran.
+La principal barrera fue la demora en la contratación del especialista y en la compra de equipos necesarios para la parte práctica de las capacitaciones. Como riesgos, se identifican posibles desfases entre la programación y ejecución de actividades técnicas, así como retrasos en los servicios y actividades previstas por demoras en contrataciones y adquisiciones.</t>
+  </si>
+  <si>
+    <t>En el primer hito se cumplió el 80% de las actividades programadas, alcanzando cuatro de cinco actividades. Destaca el desarrollo de tres protocolos y procedimientos para análisis de calidad de semillas forestales, junto con el fortalecimiento de capacidades del equipo técnico.
+Este avance permitirá optimizar procesos, mejorar la calidad del material botánico y posicionar a la UT Cajamarca como referente regional en análisis de semillas forestales, atendiendo una demanda local insatisfecha y facilitando alianzas con instituciones como SERFOR.</t>
+  </si>
+  <si>
+    <t>El proyecto busca fortalecer la competitividad de al menos 100 MYPE del sector confecciones en Lima, mediante transformación digital, desarrollo de producto y gestión comercial tecnológica.
+Durante el Hito I se ejecutaron capacitaciones y asistencias técnicas, superando metas de capacitación con 35 empresas beneficiadas y culminando servicios clave como fichas técnicas digitales, digitalización de patrones y planes de marketing digital. Asimismo, se alcanzó una ejecución financiera del 68 %, mostrando un avance físico favorable y contribuyendo al fortalecimiento de las empresas atendidas.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el proyecto del CITE Agroindustrial Majes cumplió y superó las metas técnicas programadas, brindando 57 servicios de capacitación especializada y 16 servicios de información tecnológica a unidades productivas agroindustriales de Arequipa.
+En el aspecto financiero, se ejecutaron S/ 61,954.24 de los S/ 132,200.00 programados para el hito, evidenciando un avance técnico favorable y una ejecución financiera parcial.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el proyecto consolidó la fase de diagnóstico competitivo, superando la meta al atender 97 unidades productivas frente a 65 programadas. Asimismo, se cumplieron al 100% los servicios de asistencia técnica, ensayos de laboratorio, comercio internacional y difusión inicial; y se superó la meta en diseño de envases.
+En lo financiero, se ejecutaron S/ 45,775.00, equivalente al 40% de lo programado para el hito. La menor ejecución se explica por retrasos en la contratación de servicios de terceros, aunque el CITE mantiene el compromiso de recuperar el avance en los siguientes hitos.</t>
+  </si>
+  <si>
+    <t>--Al cierre del Hito 1, el proyecto cumplió el 100% de las metas físicas programadas en las actividades vinculadas a digitalización comercial, automatización del aparado, digitalización de moldes, desarrollo de prototipos y soporte productivo.
+En lo financiero, se ejecutaron S/ 24,755.00 de los S/ 104,415.00 programados, equivalente al 24%. La menor ejecución se debe a que las partidas de materiales, insumos y equipos aún se encuentran en proceso, con órdenes vigentes dentro de los plazos establecidos.</t>
+  </si>
+  <si>
+    <t>El proyecto cumplió el 100% de las metas físicas previstas para el Hito 1 y avanzó en la contratación de servicios necesarios para su continuidad. No obstante, se registró un desfase administrativo en la formalización de órdenes de servicio, lo que afectó temporalmente la ejecución financiera. Como riesgo, persisten posibles retrasos en contrataciones futuras, por lo que se vienen realizando acciones de seguimiento para asegurar el cumplimiento de la programación.</t>
+  </si>
+  <si>
+    <t>El CITEmadera y del Mueble mostró un desempeño técnico favorable, superando las metas de diagnósticos productivos y empresas comprometidas, además de certificar el 96.25% del presupuesto asignado.
+No obstante, se identificaron demoras administrativas mayores a 30 días hábiles en validaciones y procesos de contratación, así como un déficit presupuestal que impidió adquirir una tablet de diseño. Estos retrasos representan un riesgo para el cumplimiento del cronograma y las metas de los siguientes hitos.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el CITEforestal Maynas ejecutó 39 de 40 servicios programados, alcanzando un avance físico de 97,5 % y cumpliendo el hito. Los principales logros correspondieron a ensayos de laboratorio, soporte productivo, asistencias técnicas, SIG/teledetección y diseño de productos con valor agregado. El avance financiero fue de 27 %, sustentado principalmente en contrapartida no monetaria.
+Las principales barreras fueron climáticas, logísticas y de disponibilidad de personal, lo que llevó a reprogramar los servicios pendientes al Hito 2 mediante una modificación de menor alcance, sin afectar metas ni presupuesto. El principal riesgo es la concentración de actividades en el siguiente hito, por lo que se aplicará una programación escalonada por componente y zona de intervención.</t>
+  </si>
+  <si>
+    <t>Al cierre del Hito 1, el proyecto cumplió el 100% de las metas físicas programadas en actividades de digitalización comercial, automatización del aparado, digitalización de moldes, prototipos y soporte productivo.
+En lo financiero, se ejecutaron S/ 24,755.00 de S/ 104,415.00 programados, equivalente al 24%. La menor ejecución se debe a que las partidas de materiales, insumos y equipos aún no registran gasto, aunque las órdenes se encuentran vigentes y dentro de plazo.</t>
+  </si>
+  <si>
+    <t>Durante el Hito 1, el proyecto avanzó en el fortalecimiento de capacidades productivas de UP de primera y segunda transformación de la madera. Se cumplió al 100 % la asistencia técnica para la construcción e implementación de la hoja de ruta de intervención descentralizada, identificando seis productos terminados priorizados, y se desarrolló una charla técnica de información tecnológica especializada dirigida a 30 UP del sector forestal.
+En el aspecto financiero, la ejecución fue parcial debido a que los servicios se encuentran dentro del plazo contractual y en proceso administrativo de pago. No obstante, las actividades se desarrollan conforme a la programación, sin afectar el cumplimiento de los objetivos y metas del hito.</t>
+  </si>
+  <si>
+    <t>Presupuesto modificado (MMA)</t>
+  </si>
+  <si>
+    <t>Monto desembolsado según resolución</t>
   </si>
 </sst>
 </file>
@@ -330,13 +350,20 @@
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;S/&quot;\ #,##0.00;[Red]\-&quot;S/&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -380,13 +407,26 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -426,9 +466,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -437,29 +477,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -696,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
@@ -705,17 +753,18 @@
     <col min="4" max="4" width="9.109375" customWidth="1"/>
     <col min="5" max="7" width="12.33203125" customWidth="1"/>
     <col min="8" max="9" width="12.33203125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="13" width="14.88671875" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" customWidth="1"/>
-    <col min="18" max="18" width="42.6640625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="42.6640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="14" width="14.88671875" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" customWidth="1"/>
+    <col min="16" max="16" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" customWidth="1"/>
+    <col min="19" max="19" width="42.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="42.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -731,50 +780,53 @@
       <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>46</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -788,52 +840,55 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2" s="18">
         <v>2</v>
       </c>
+      <c r="F2" s="17">
+        <v>2</v>
+      </c>
       <c r="G2" s="12">
-        <v>0.66700000000000004</v>
+        <v>1</v>
       </c>
       <c r="H2" s="9">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I2" s="9">
-        <v>13</v>
-      </c>
-      <c r="J2" s="13">
+        <v>15</v>
+      </c>
+      <c r="J2" s="20">
         <v>230221</v>
       </c>
       <c r="K2" s="13">
-        <v>230125</v>
+        <v>230220.62</v>
       </c>
       <c r="L2" s="13">
+        <v>230221</v>
+      </c>
+      <c r="M2" s="13">
         <v>10750</v>
       </c>
-      <c r="M2" s="13">
-        <v>8238</v>
-      </c>
-      <c r="N2" s="11">
+      <c r="N2" s="13">
+        <v>9475</v>
+      </c>
+      <c r="O2" s="11">
         <v>1</v>
       </c>
-      <c r="O2" s="11">
+      <c r="P2" s="11">
         <v>4.7E-2</v>
       </c>
-      <c r="P2" s="11">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="11">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="R2" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S2" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -847,46 +902,47 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="18">
         <v>0</v>
       </c>
-      <c r="G3" s="12">
+      <c r="F3" s="17">
         <v>0</v>
       </c>
-      <c r="J3" s="13">
+      <c r="G3" s="12"/>
+      <c r="J3" s="20">
         <v>223105</v>
       </c>
       <c r="K3" s="13">
-        <v>26758</v>
+        <v>223104.83</v>
       </c>
       <c r="L3" s="13">
-        <v>21778</v>
+        <v>96524</v>
       </c>
       <c r="M3" s="13">
+        <v>34511</v>
+      </c>
+      <c r="N3" s="13">
         <v>1400</v>
       </c>
-      <c r="N3" s="11">
-        <v>0.12</v>
-      </c>
       <c r="O3" s="11">
-        <v>9.8000000000000004E-2</v>
+        <v>0.433</v>
       </c>
       <c r="P3" s="11">
+        <v>0.155</v>
+      </c>
+      <c r="Q3" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -900,46 +956,55 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>13</v>
-      </c>
-      <c r="F4" s="18">
         <v>6</v>
       </c>
+      <c r="F4" s="17">
+        <v>3</v>
+      </c>
       <c r="G4" s="12">
-        <v>0.46200000000000002</v>
-      </c>
-      <c r="J4" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="9">
+        <v>35</v>
+      </c>
+      <c r="I4" s="9">
+        <v>10</v>
+      </c>
+      <c r="J4" s="20">
         <v>217442</v>
       </c>
       <c r="K4" s="13">
+        <v>145441.56</v>
+      </c>
+      <c r="L4" s="13">
+        <v>90152</v>
+      </c>
+      <c r="M4" s="13">
         <v>87580</v>
       </c>
-      <c r="L4" s="13">
-        <v>87580</v>
-      </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>0</v>
       </c>
-      <c r="N4" s="11">
-        <v>0.40300000000000002</v>
-      </c>
       <c r="O4" s="11">
-        <v>0.40300000000000002</v>
+        <v>0.62</v>
       </c>
       <c r="P4" s="11">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="Q4" s="11">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -953,46 +1018,47 @@
         <v>13</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" s="18">
         <v>0</v>
       </c>
-      <c r="G5" s="12">
+      <c r="F5" s="17">
         <v>0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="G5" s="12"/>
+      <c r="J5" s="20">
         <v>159704</v>
       </c>
       <c r="K5" s="13">
-        <v>116743</v>
+        <v>159704</v>
       </c>
       <c r="L5" s="13">
-        <v>116743</v>
+        <v>151046.29</v>
       </c>
       <c r="M5" s="13">
-        <v>24898</v>
-      </c>
-      <c r="N5" s="11">
-        <v>0.73099999999999998</v>
+        <v>144564.29</v>
+      </c>
+      <c r="N5" s="13">
+        <v>28925.72</v>
       </c>
       <c r="O5" s="11">
-        <v>0.73099999999999998</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="P5" s="11">
-        <v>0.156</v>
-      </c>
-      <c r="Q5" t="s">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="R5" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S5" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1006,52 +1072,55 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6" s="18">
         <v>12</v>
       </c>
+      <c r="F6" s="17">
+        <v>10</v>
+      </c>
       <c r="G6" s="12">
-        <v>0.85699999999999998</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="H6" s="9">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="I6" s="9">
-        <v>105</v>
-      </c>
-      <c r="J6" s="13">
+        <v>147</v>
+      </c>
+      <c r="J6" s="20">
         <v>158350</v>
       </c>
       <c r="K6" s="13">
-        <v>79392</v>
+        <v>158350</v>
       </c>
       <c r="L6" s="13">
-        <v>79392</v>
+        <v>104223</v>
       </c>
       <c r="M6" s="13">
-        <v>11802</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0.501</v>
+        <v>96505</v>
+      </c>
+      <c r="N6" s="13">
+        <v>17215</v>
       </c>
       <c r="O6" s="11">
-        <v>0.501</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="P6" s="11">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="Q6" t="s">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0.109</v>
+      </c>
+      <c r="R6" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1065,52 +1134,55 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7" s="18">
         <v>6</v>
       </c>
+      <c r="F7" s="17">
+        <v>6</v>
+      </c>
       <c r="G7" s="12">
-        <v>0.85699999999999998</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I7" s="9">
-        <v>20</v>
-      </c>
-      <c r="J7" s="13">
-        <v>156838</v>
+        <v>44</v>
+      </c>
+      <c r="J7" s="20">
+        <v>156837.92000000001</v>
       </c>
       <c r="K7" s="13">
+        <v>156837.91</v>
+      </c>
+      <c r="L7" s="13">
+        <v>122480</v>
+      </c>
+      <c r="M7" s="13">
         <v>112636</v>
       </c>
-      <c r="L7" s="13">
-        <v>112636</v>
-      </c>
-      <c r="M7" s="13">
-        <v>21968</v>
-      </c>
-      <c r="N7" s="11">
+      <c r="N7" s="13">
+        <v>25367.52</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="P7" s="11">
         <v>0.71799999999999997</v>
       </c>
-      <c r="O7" s="11">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="11">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="R7" t="s">
         <v>38</v>
       </c>
-      <c r="R7" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1124,46 +1196,47 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" s="18">
         <v>0</v>
       </c>
-      <c r="G8" s="12">
+      <c r="F8" s="17">
         <v>0</v>
       </c>
-      <c r="J8" s="13">
-        <v>147913</v>
+      <c r="G8" s="12"/>
+      <c r="J8" s="20">
+        <v>151913</v>
       </c>
       <c r="K8" s="13">
-        <v>21617</v>
+        <v>151914</v>
       </c>
       <c r="L8" s="13">
-        <v>21611</v>
+        <v>47641</v>
       </c>
       <c r="M8" s="13">
-        <v>12494</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.14599999999999999</v>
+        <v>36611</v>
+      </c>
+      <c r="N8" s="13">
+        <v>12869</v>
       </c>
       <c r="O8" s="11">
-        <v>0.14599999999999999</v>
+        <v>0.314</v>
       </c>
       <c r="P8" s="11">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="Q8" t="s">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="R8" t="s">
         <v>38</v>
       </c>
-      <c r="R8" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S8" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1179,44 +1252,53 @@
       <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>4</v>
       </c>
       <c r="G9" s="12">
-        <v>1</v>
-      </c>
-      <c r="J9" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="9">
+        <v>29</v>
+      </c>
+      <c r="I9" s="9">
+        <v>29</v>
+      </c>
+      <c r="J9" s="20">
         <v>109375</v>
       </c>
       <c r="K9" s="13">
+        <v>109375</v>
+      </c>
+      <c r="L9" s="13">
+        <v>46962</v>
+      </c>
+      <c r="M9" s="13">
         <v>45000</v>
       </c>
-      <c r="L9" s="13">
-        <v>45000</v>
-      </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="O9" s="11">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="P9" s="11">
         <v>0.41099999999999998</v>
       </c>
-      <c r="O9" s="11">
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="P9" s="11">
+      <c r="Q9" s="11">
         <v>0</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>38</v>
       </c>
-      <c r="R9" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S9" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1230,46 +1312,55 @@
         <v>13</v>
       </c>
       <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10" s="18">
+        <v>6</v>
+      </c>
+      <c r="F10" s="17">
         <v>6</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
       </c>
-      <c r="J10" s="13">
-        <v>103175</v>
+      <c r="H10" s="9">
+        <v>45</v>
+      </c>
+      <c r="I10" s="9">
+        <v>38</v>
+      </c>
+      <c r="J10" s="20">
+        <v>109175</v>
       </c>
       <c r="K10" s="13">
-        <v>52874</v>
+        <v>95775</v>
       </c>
       <c r="L10" s="13">
-        <v>52874</v>
+        <v>104119.65</v>
       </c>
       <c r="M10" s="13">
-        <v>38594</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0.51200000000000001</v>
+        <v>57873.8</v>
+      </c>
+      <c r="N10" s="13">
+        <v>38593.800000000003</v>
       </c>
       <c r="O10" s="11">
-        <v>0.51200000000000001</v>
+        <v>1.087</v>
       </c>
       <c r="P10" s="11">
-        <v>0.374</v>
-      </c>
-      <c r="Q10" t="s">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="R10" t="s">
         <v>38</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1285,47 +1376,50 @@
       <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>4</v>
       </c>
       <c r="G11" s="12">
         <v>1</v>
       </c>
       <c r="H11" s="9">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="I11" s="9">
-        <v>7</v>
-      </c>
-      <c r="J11" s="13">
+        <v>71</v>
+      </c>
+      <c r="J11" s="20">
         <v>96950</v>
       </c>
       <c r="K11" s="13">
-        <v>96355</v>
+        <v>96950</v>
       </c>
       <c r="L11" s="13">
-        <v>96355</v>
+        <v>96860.14</v>
       </c>
       <c r="M11" s="13">
-        <v>23736</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0.99399999999999999</v>
+        <v>96860.14</v>
+      </c>
+      <c r="N11" s="13">
+        <v>28736.240000000002</v>
       </c>
       <c r="O11" s="11">
-        <v>0.99399999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="P11" s="11">
-        <v>0.245</v>
-      </c>
-      <c r="Q11" t="s">
+        <v>0.999</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="R11" t="s">
         <v>39</v>
       </c>
-      <c r="S11" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T11" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1341,11 +1435,11 @@
       <c r="E12">
         <v>3</v>
       </c>
-      <c r="F12" s="18">
-        <v>3</v>
+      <c r="F12" s="17">
+        <v>2</v>
       </c>
       <c r="G12" s="12">
-        <v>1</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="H12" s="9">
         <v>88</v>
@@ -1353,35 +1447,35 @@
       <c r="I12" s="9">
         <v>67</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="20">
         <v>96875</v>
       </c>
       <c r="K12" s="13">
-        <v>85400</v>
+        <v>87500</v>
       </c>
       <c r="L12" s="13">
-        <v>85400</v>
+        <v>87700</v>
       </c>
       <c r="M12" s="13">
+        <v>87000</v>
+      </c>
+      <c r="N12" s="13">
         <v>59000</v>
       </c>
-      <c r="N12" s="11">
-        <v>0.88200000000000001</v>
-      </c>
       <c r="O12" s="11">
-        <v>0.88200000000000001</v>
+        <v>1.002</v>
       </c>
       <c r="P12" s="11">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="Q12" t="s">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="R12" t="s">
         <v>39</v>
       </c>
-      <c r="S12" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1397,47 +1491,50 @@
       <c r="E13">
         <v>12</v>
       </c>
-      <c r="F13" s="18">
-        <v>12</v>
+      <c r="F13" s="17">
+        <v>8</v>
       </c>
       <c r="G13" s="12">
-        <v>1</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="H13" s="9">
-        <v>115</v>
+        <v>248</v>
       </c>
       <c r="I13" s="9">
-        <v>74</v>
-      </c>
-      <c r="J13" s="13">
+        <v>96</v>
+      </c>
+      <c r="J13" s="20">
+        <v>96775</v>
+      </c>
+      <c r="K13" s="13">
         <v>95775</v>
-      </c>
-      <c r="K13" s="13">
-        <v>87700</v>
       </c>
       <c r="L13" s="13">
         <v>87700</v>
       </c>
       <c r="M13" s="13">
+        <v>87700</v>
+      </c>
+      <c r="N13" s="13">
         <v>25900</v>
-      </c>
-      <c r="N13" s="11">
-        <v>0.91600000000000004</v>
       </c>
       <c r="O13" s="11">
         <v>0.91600000000000004</v>
       </c>
       <c r="P13" s="11">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="Q13" s="11">
         <v>0.27</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>39</v>
       </c>
-      <c r="S13" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T13" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1453,41 +1550,50 @@
       <c r="E14">
         <v>5</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>5</v>
       </c>
       <c r="G14" s="12">
         <v>1</v>
       </c>
-      <c r="J14" s="13">
+      <c r="H14" s="9">
+        <v>6</v>
+      </c>
+      <c r="I14" s="9">
+        <v>2</v>
+      </c>
+      <c r="J14" s="20">
         <v>89665</v>
       </c>
       <c r="K14" s="13">
-        <v>65474</v>
+        <v>88115</v>
       </c>
       <c r="L14" s="13">
-        <v>60075</v>
+        <v>65212.43</v>
       </c>
       <c r="M14" s="13">
-        <v>8910</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0.73</v>
+        <v>65212.43</v>
+      </c>
+      <c r="N14" s="13">
+        <v>84.46</v>
       </c>
       <c r="O14" s="11">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="P14" s="11">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="Q14" t="s">
+        <v>0.74</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>1E-3</v>
+      </c>
+      <c r="R14" t="s">
         <v>39</v>
       </c>
-      <c r="S14" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T14" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1501,46 +1607,52 @@
         <v>13</v>
       </c>
       <c r="E15">
-        <v>8</v>
-      </c>
-      <c r="F15" s="18">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F15" s="17">
+        <v>9</v>
       </c>
       <c r="G15" s="12">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H15" s="9">
-        <v>540</v>
+        <v>651</v>
       </c>
       <c r="I15" s="9">
-        <v>22</v>
-      </c>
-      <c r="J15" s="13">
+        <v>46</v>
+      </c>
+      <c r="J15" s="20">
         <v>78375</v>
       </c>
       <c r="K15" s="13">
+        <v>78375</v>
+      </c>
+      <c r="L15" s="13">
+        <v>69000</v>
+      </c>
+      <c r="M15" s="13">
         <v>67950</v>
       </c>
-      <c r="L15" s="13">
-        <v>67950</v>
-      </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>41300</v>
       </c>
-      <c r="N15" s="11">
+      <c r="O15" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="P15" s="11">
         <v>0.86699999999999999</v>
       </c>
-      <c r="O15" s="11">
-        <v>0.86699999999999999</v>
-      </c>
-      <c r="P15" s="11">
+      <c r="Q15" s="11">
         <v>0.52700000000000002</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T15" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1554,46 +1666,55 @@
         <v>13</v>
       </c>
       <c r="E16">
-        <v>4</v>
-      </c>
-      <c r="F16" s="18">
         <v>2</v>
       </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
       <c r="G16" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>22</v>
+      </c>
+      <c r="I16" s="9">
+        <v>22</v>
+      </c>
+      <c r="J16" s="20">
         <v>70675</v>
       </c>
       <c r="K16" s="13">
-        <v>64403</v>
+        <v>70675</v>
       </c>
       <c r="L16" s="13">
-        <v>64403</v>
+        <v>64051.75</v>
       </c>
       <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0.91100000000000003</v>
+        <v>61380.75</v>
+      </c>
+      <c r="N16" s="13">
+        <v>10609.5</v>
       </c>
       <c r="O16" s="11">
-        <v>0.91100000000000003</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="R16" t="s">
         <v>38</v>
       </c>
-      <c r="R16" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S16" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1607,52 +1728,55 @@
         <v>13</v>
       </c>
       <c r="E17">
-        <v>13</v>
-      </c>
-      <c r="F17" s="18">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F17" s="17">
+        <v>8</v>
       </c>
       <c r="G17" s="12">
-        <v>0.53800000000000003</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="H17" s="9">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="I17" s="9">
-        <v>5</v>
-      </c>
-      <c r="J17" s="13">
+        <v>11</v>
+      </c>
+      <c r="J17" s="20">
         <v>56175</v>
       </c>
       <c r="K17" s="13">
-        <v>45000</v>
+        <v>56175</v>
       </c>
       <c r="L17" s="13">
         <v>45000</v>
       </c>
       <c r="M17" s="13">
+        <v>45000</v>
+      </c>
+      <c r="N17" s="13">
         <v>0</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0.80100000000000005</v>
       </c>
       <c r="O17" s="11">
         <v>0.80100000000000005</v>
       </c>
       <c r="P17" s="11">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="Q17" s="11">
         <v>0</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>38</v>
       </c>
-      <c r="R17" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S17" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S17" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1666,52 +1790,55 @@
         <v>13</v>
       </c>
       <c r="E18">
-        <v>8</v>
-      </c>
-      <c r="F18" s="18">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F18" s="17">
+        <v>6</v>
       </c>
       <c r="G18" s="12">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="H18" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I18" s="9">
-        <v>6</v>
-      </c>
-      <c r="J18" s="13">
+        <v>9</v>
+      </c>
+      <c r="J18" s="20">
+        <v>40974.79</v>
+      </c>
+      <c r="K18" s="13">
         <v>40975</v>
       </c>
-      <c r="K18" s="13">
-        <v>26000</v>
-      </c>
       <c r="L18" s="13">
-        <v>26000</v>
+        <v>30100</v>
       </c>
       <c r="M18" s="13">
-        <v>5500</v>
-      </c>
-      <c r="N18" s="11">
-        <v>0.63500000000000001</v>
+        <v>29600</v>
+      </c>
+      <c r="N18" s="13">
+        <v>8455</v>
       </c>
       <c r="O18" s="11">
-        <v>0.63500000000000001</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="P18" s="11">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="Q18" t="s">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="R18" t="s">
         <v>38</v>
       </c>
-      <c r="R18" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S18" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1727,38 +1854,47 @@
       <c r="E19">
         <v>2</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>2</v>
       </c>
       <c r="G19" s="12">
         <v>1</v>
       </c>
-      <c r="J19" s="13">
-        <v>19131</v>
+      <c r="H19" s="9">
+        <v>30</v>
+      </c>
+      <c r="I19" s="9">
+        <v>30</v>
+      </c>
+      <c r="J19" s="20">
+        <v>21631</v>
       </c>
       <c r="K19" s="13">
+        <v>21631</v>
+      </c>
+      <c r="L19" s="13">
+        <v>16205</v>
+      </c>
+      <c r="M19" s="13">
         <v>12925</v>
       </c>
-      <c r="L19" s="13">
-        <v>12925</v>
-      </c>
-      <c r="M19" s="13">
+      <c r="N19" s="13">
         <v>2000</v>
       </c>
-      <c r="N19" s="11">
-        <v>0.67600000000000005</v>
-      </c>
       <c r="O19" s="11">
-        <v>0.67600000000000005</v>
+        <v>0.749</v>
       </c>
       <c r="P19" s="11">
-        <v>0.105</v>
-      </c>
-      <c r="Q19" t="s">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="R19" t="s">
         <v>39</v>
       </c>
-      <c r="S19" s="5" t="s">
-        <v>66</v>
+      <c r="T19" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1769,13 +1905,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A138854-8EA5-422D-AA90-16741E68D00C}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1783,116 +1920,125 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="26"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>89</v>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\seguimiento_cdd_fest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF264C2E-656E-4436-8410-476A383E3D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1055E5AC-6BDE-4046-B787-01AE8126D196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -1669,10 +1669,10 @@
         <v>2</v>
       </c>
       <c r="F16" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="9">
         <v>22</v>
